--- a/results/latest.xlsx
+++ b/results/latest.xlsx
@@ -904,13 +904,13 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>BCPC</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CUBE</t>
+          <t>CVCO</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BCPC</t>
+          <t>BCRX</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CVCO</t>
+          <t>CVSA</t>
         </is>
       </c>
     </row>
@@ -934,13 +934,13 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BCRX</t>
+          <t>BHP</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CVSA</t>
+          <t>DAR</t>
         </is>
       </c>
     </row>
@@ -949,13 +949,13 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BHP</t>
+          <t>BIIB</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DAR</t>
+          <t>DASH</t>
         </is>
       </c>
     </row>
@@ -964,13 +964,13 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DASH</t>
+          <t>DC</t>
         </is>
       </c>
     </row>
@@ -979,13 +979,13 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>BP</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DC</t>
+          <t>DINO</t>
         </is>
       </c>
     </row>
@@ -994,13 +994,13 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BP</t>
+          <t>BTE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>DRH</t>
         </is>
       </c>
     </row>
@@ -1009,13 +1009,13 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BTE</t>
+          <t>CADL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DRH</t>
+          <t>ECL</t>
         </is>
       </c>
     </row>
@@ -1024,13 +1024,13 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CADL</t>
+          <t>CART</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>ECL</t>
+          <t>EGO</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1039,13 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CART</t>
+          <t>CBRE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EGO</t>
+          <t>ELS</t>
         </is>
       </c>
     </row>
@@ -1054,13 +1054,13 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CBRE</t>
+          <t>CGON</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ELS</t>
+          <t>EMBJ</t>
         </is>
       </c>
     </row>
@@ -1069,13 +1069,13 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CGON</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EMBJ</t>
+          <t>EQIX</t>
         </is>
       </c>
     </row>
@@ -1084,13 +1084,13 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CHRD</t>
+          <t>CLH</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EQIX</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
@@ -1099,13 +1099,13 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLH</t>
+          <t>CLYM</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ET</t>
+          <t>EW</t>
         </is>
       </c>
     </row>
@@ -1114,13 +1114,13 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLYM</t>
+          <t>CMBT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EW</t>
+          <t>EXK</t>
         </is>
       </c>
     </row>
@@ -1129,13 +1129,13 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CMBT</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>EXK</t>
+          <t>EXPD</t>
         </is>
       </c>
     </row>
@@ -1144,13 +1144,13 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CORT</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>EXPD</t>
+          <t>FIGS</t>
         </is>
       </c>
     </row>
@@ -1159,13 +1159,13 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CORT</t>
+          <t>CRGY</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FCFS</t>
+          <t>FOX</t>
         </is>
       </c>
     </row>
@@ -1174,13 +1174,13 @@
       <c r="B44" t="inlineStr"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CRGY</t>
+          <t>CRON</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FIGS</t>
+          <t>FOXA</t>
         </is>
       </c>
     </row>
@@ -1189,13 +1189,13 @@
       <c r="B45" t="inlineStr"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CVE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FOX</t>
+          <t>GKOS</t>
         </is>
       </c>
     </row>
@@ -1204,13 +1204,13 @@
       <c r="B46" t="inlineStr"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CVE</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FOXA</t>
+          <t>GLNG</t>
         </is>
       </c>
     </row>
@@ -1219,13 +1219,13 @@
       <c r="B47" t="inlineStr"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>CWK</t>
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GKOS</t>
+          <t>GOLD</t>
         </is>
       </c>
     </row>
@@ -1234,13 +1234,13 @@
       <c r="B48" t="inlineStr"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CWK</t>
+          <t>DHT</t>
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GLNG</t>
+          <t>GPCR</t>
         </is>
       </c>
     </row>
@@ -1249,13 +1249,13 @@
       <c r="B49" t="inlineStr"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DHT</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GOLD</t>
+          <t>GTE</t>
         </is>
       </c>
     </row>
@@ -1264,13 +1264,13 @@
       <c r="B50" t="inlineStr"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>DNLI</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>GPCR</t>
+          <t>HASI</t>
         </is>
       </c>
     </row>
@@ -1279,13 +1279,13 @@
       <c r="B51" t="inlineStr"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DNLI</t>
+          <t>DSX</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>GTE</t>
+          <t>HBM</t>
         </is>
       </c>
     </row>
@@ -1294,13 +1294,13 @@
       <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DSX</t>
+          <t>DUOT</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>HASI</t>
+          <t>HLN</t>
         </is>
       </c>
     </row>
@@ -1309,13 +1309,13 @@
       <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DUOT</t>
+          <t>DVN</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HBM</t>
+          <t>HLX</t>
         </is>
       </c>
     </row>
@@ -1324,13 +1324,13 @@
       <c r="B54" t="inlineStr"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DVN</t>
+          <t>DX</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>HLN</t>
+          <t>HP</t>
         </is>
       </c>
     </row>
@@ -1339,13 +1339,13 @@
       <c r="B55" t="inlineStr"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DX</t>
+          <t>EC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HLX</t>
+          <t>HZO</t>
         </is>
       </c>
     </row>
@@ -1354,13 +1354,13 @@
       <c r="B56" t="inlineStr"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EC</t>
+          <t>ECO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HP</t>
+          <t>IAUX</t>
         </is>
       </c>
     </row>
@@ -1369,13 +1369,13 @@
       <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ECO</t>
+          <t>EFC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HZO</t>
+          <t>ICUI</t>
         </is>
       </c>
     </row>
@@ -1384,13 +1384,13 @@
       <c r="B58" t="inlineStr"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>EFC</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAUX</t>
+          <t>IHS</t>
         </is>
       </c>
     </row>
@@ -1399,13 +1399,13 @@
       <c r="B59" t="inlineStr"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ICUI</t>
+          <t>ILMN</t>
         </is>
       </c>
     </row>
@@ -1414,13 +1414,13 @@
       <c r="B60" t="inlineStr"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>EQNR</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IHS</t>
+          <t>IMAX</t>
         </is>
       </c>
     </row>
@@ -1429,13 +1429,13 @@
       <c r="B61" t="inlineStr"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EQNR</t>
+          <t>ETON</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>ITIC</t>
         </is>
       </c>
     </row>
@@ -1444,13 +1444,13 @@
       <c r="B62" t="inlineStr"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ETON</t>
+          <t>EWTX</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IMAX</t>
+          <t>LOAR</t>
         </is>
       </c>
     </row>
@@ -1459,13 +1459,13 @@
       <c r="B63" t="inlineStr"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>EWTX</t>
+          <t>FANG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ITIC</t>
+          <t>LTC</t>
         </is>
       </c>
     </row>
@@ -1474,13 +1474,13 @@
       <c r="B64" t="inlineStr"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FANG</t>
+          <t>FCX</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>LOAR</t>
+          <t>LXRX</t>
         </is>
       </c>
     </row>
@@ -1489,13 +1489,13 @@
       <c r="B65" t="inlineStr"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FCX</t>
+          <t>FLR</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>LTC</t>
+          <t>MATX</t>
         </is>
       </c>
     </row>
@@ -1504,13 +1504,13 @@
       <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>FLR</t>
+          <t>FNV</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LXRX</t>
+          <t>MEOH</t>
         </is>
       </c>
     </row>
@@ -1519,13 +1519,13 @@
       <c r="B67" t="inlineStr"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FNV</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MATX</t>
+          <t>MGA</t>
         </is>
       </c>
     </row>
@@ -1534,13 +1534,13 @@
       <c r="B68" t="inlineStr"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>FRNM</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEOH</t>
+          <t>MPC</t>
         </is>
       </c>
     </row>
@@ -1549,13 +1549,13 @@
       <c r="B69" t="inlineStr"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MGA</t>
+          <t>MRAM</t>
         </is>
       </c>
     </row>
@@ -1564,13 +1564,13 @@
       <c r="B70" t="inlineStr"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MPC</t>
+          <t>MRX</t>
         </is>
       </c>
     </row>
@@ -1579,13 +1579,13 @@
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FSM</t>
+          <t>FWONK</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MRAM</t>
+          <t>MSI</t>
         </is>
       </c>
     </row>
@@ -1594,13 +1594,13 @@
       <c r="B72" t="inlineStr"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FWONK</t>
+          <t>GILD</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MRX</t>
+          <t>MU</t>
         </is>
       </c>
     </row>
@@ -1609,13 +1609,13 @@
       <c r="B73" t="inlineStr"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>GMAB</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>MSI</t>
+          <t>NSC</t>
         </is>
       </c>
     </row>
@@ -1624,13 +1624,13 @@
       <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MU</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
@@ -1639,13 +1639,13 @@
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>HAE</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>NSC</t>
+          <t>NWE</t>
         </is>
       </c>
     </row>
@@ -1654,13 +1654,13 @@
       <c r="B76" t="inlineStr"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HAE</t>
+          <t>HAFN</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>OMC</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HAFN</t>
+          <t>HALO</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>NWE</t>
+          <t>PAA</t>
         </is>
       </c>
     </row>
@@ -1684,13 +1684,13 @@
       <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HALO</t>
+          <t>HCC</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>OMC</t>
+          <t>PBR</t>
         </is>
       </c>
     </row>
@@ -1699,13 +1699,13 @@
       <c r="B79" t="inlineStr"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>HCC</t>
+          <t>HMY</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>PDM</t>
         </is>
       </c>
     </row>
@@ -1714,13 +1714,13 @@
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>HMY</t>
+          <t>HRMY</t>
         </is>
       </c>
       <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
-          <t>PBR</t>
+          <t>PEN</t>
         </is>
       </c>
     </row>
@@ -1729,13 +1729,13 @@
       <c r="B81" t="inlineStr"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HRMY</t>
+          <t>HTGC</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PDM</t>
+          <t>PHM</t>
         </is>
       </c>
     </row>
@@ -1744,13 +1744,13 @@
       <c r="B82" t="inlineStr"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>HTGC</t>
+          <t>IAG</t>
         </is>
       </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PEN</t>
+          <t>PM</t>
         </is>
       </c>
     </row>
@@ -1759,13 +1759,13 @@
       <c r="B83" t="inlineStr"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IAG</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>PHM</t>
+          <t>PRAX</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
       <c r="B84" t="inlineStr"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>IDYA</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
-          <t>PM</t>
+          <t>PRCH</t>
         </is>
       </c>
     </row>
@@ -1789,13 +1789,13 @@
       <c r="B85" t="inlineStr"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IDYA</t>
+          <t>IMMX</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PRAX</t>
+          <t>PSX</t>
         </is>
       </c>
     </row>
@@ -1804,13 +1804,13 @@
       <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>IMMX</t>
+          <t>IMNM</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>PRCH</t>
+          <t>QSR</t>
         </is>
       </c>
     </row>
@@ -1819,13 +1819,13 @@
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>IMNM</t>
+          <t>IMO</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
-          <t>PSX</t>
+          <t>REAL</t>
         </is>
       </c>
     </row>
@@ -1834,13 +1834,13 @@
       <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>IMO</t>
+          <t>IMVT</t>
         </is>
       </c>
       <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>QSR</t>
+          <t>RIG</t>
         </is>
       </c>
     </row>
@@ -1849,13 +1849,13 @@
       <c r="B89" t="inlineStr"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>IMVT</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RIG</t>
+          <t>RYAM</t>
         </is>
       </c>
     </row>
@@ -1864,13 +1864,13 @@
       <c r="B90" t="inlineStr"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>INBX</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RYAM</t>
+          <t>SA</t>
         </is>
       </c>
     </row>
@@ -1879,13 +1879,13 @@
       <c r="B91" t="inlineStr"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>INSW</t>
         </is>
       </c>
       <c r="D91" t="inlineStr"/>
       <c r="E91" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>SAIC</t>
         </is>
       </c>
     </row>
@@ -1894,13 +1894,13 @@
       <c r="B92" t="inlineStr"/>
       <c r="C92" t="inlineStr">
         <is>
-          <t>INSW</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SAIC</t>
+          <t>SBRA</t>
         </is>
       </c>
     </row>
@@ -1909,13 +1909,13 @@
       <c r="B93" t="inlineStr"/>
       <c r="C93" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>JNJ</t>
         </is>
       </c>
       <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SBRA</t>
+          <t>SGMT</t>
         </is>
       </c>
     </row>
@@ -1924,13 +1924,13 @@
       <c r="B94" t="inlineStr"/>
       <c r="C94" t="inlineStr">
         <is>
-          <t>JNJ</t>
+          <t>KNTK</t>
         </is>
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SGMT</t>
+          <t>SKM</t>
         </is>
       </c>
     </row>
@@ -1939,13 +1939,13 @@
       <c r="B95" t="inlineStr"/>
       <c r="C95" t="inlineStr">
         <is>
-          <t>KNTK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>SJM</t>
+          <t>SLAB</t>
         </is>
       </c>
     </row>
@@ -1954,13 +1954,13 @@
       <c r="B96" t="inlineStr"/>
       <c r="C96" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>KYMR</t>
         </is>
       </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>SKM</t>
+          <t>SLB</t>
         </is>
       </c>
     </row>
@@ -1969,13 +1969,13 @@
       <c r="B97" t="inlineStr"/>
       <c r="C97" t="inlineStr">
         <is>
-          <t>KYMR</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>SOLV</t>
         </is>
       </c>
     </row>
@@ -1984,13 +1984,13 @@
       <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LAUR</t>
+          <t>LB</t>
         </is>
       </c>
       <c r="D98" t="inlineStr"/>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>STLN</t>
         </is>
       </c>
     </row>
@@ -1999,13 +1999,13 @@
       <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>LB</t>
+          <t>LFST</t>
         </is>
       </c>
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>SOLV</t>
+          <t>STNG</t>
         </is>
       </c>
     </row>
@@ -2014,13 +2014,13 @@
       <c r="B100" t="inlineStr"/>
       <c r="C100" t="inlineStr">
         <is>
-          <t>LFST</t>
+          <t>LIVN</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>SVM</t>
         </is>
       </c>
     </row>
@@ -2029,13 +2029,13 @@
       <c r="B101" t="inlineStr"/>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LIVN</t>
+          <t>LLY</t>
         </is>
       </c>
       <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>STNG</t>
+          <t>SWX</t>
         </is>
       </c>
     </row>
@@ -2044,13 +2044,13 @@
       <c r="B102" t="inlineStr"/>
       <c r="C102" t="inlineStr">
         <is>
-          <t>LLY</t>
+          <t>LNG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>SXT</t>
         </is>
       </c>
     </row>
@@ -2059,13 +2059,13 @@
       <c r="B103" t="inlineStr"/>
       <c r="C103" t="inlineStr">
         <is>
-          <t>LNG</t>
+          <t>LPG</t>
         </is>
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>SWX</t>
+          <t>TDW</t>
         </is>
       </c>
     </row>
@@ -2074,13 +2074,13 @@
       <c r="B104" t="inlineStr"/>
       <c r="C104" t="inlineStr">
         <is>
-          <t>LPG</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
-          <t>SXT</t>
+          <t>TEVA</t>
         </is>
       </c>
     </row>
@@ -2089,13 +2089,13 @@
       <c r="B105" t="inlineStr"/>
       <c r="C105" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>MCO</t>
         </is>
       </c>
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TDW</t>
+          <t>TH</t>
         </is>
       </c>
     </row>
@@ -2104,13 +2104,13 @@
       <c r="B106" t="inlineStr"/>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>MDT</t>
         </is>
       </c>
       <c r="D106" t="inlineStr"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>TEVA</t>
+          <t>THM</t>
         </is>
       </c>
     </row>
@@ -2119,13 +2119,13 @@
       <c r="B107" t="inlineStr"/>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MDT</t>
+          <t>MGTX</t>
         </is>
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>TPG</t>
         </is>
       </c>
     </row>
@@ -2134,13 +2134,13 @@
       <c r="B108" t="inlineStr"/>
       <c r="C108" t="inlineStr">
         <is>
-          <t>MGTX</t>
+          <t>MHO</t>
         </is>
       </c>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
-          <t>THM</t>
+          <t>U</t>
         </is>
       </c>
     </row>
@@ -2149,13 +2149,13 @@
       <c r="B109" t="inlineStr"/>
       <c r="C109" t="inlineStr">
         <is>
-          <t>MHO</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
-          <t>TPG</t>
+          <t>UL</t>
         </is>
       </c>
     </row>
@@ -2164,13 +2164,13 @@
       <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>MRNA</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
       <c r="E110" t="inlineStr">
         <is>
-          <t>U</t>
+          <t>UNP</t>
         </is>
       </c>
     </row>
@@ -2179,13 +2179,13 @@
       <c r="B111" t="inlineStr"/>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MRNA</t>
+          <t>MRVL</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
       <c r="E111" t="inlineStr">
         <is>
-          <t>UL</t>
+          <t>URGN</t>
         </is>
       </c>
     </row>
@@ -2194,13 +2194,13 @@
       <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>MTA</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>UNP</t>
+          <t>VAL</t>
         </is>
       </c>
     </row>
@@ -2209,13 +2209,13 @@
       <c r="B113" t="inlineStr"/>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MTA</t>
+          <t>MTDR</t>
         </is>
       </c>
       <c r="D113" t="inlineStr"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>URGN</t>
+          <t>VIRT</t>
         </is>
       </c>
     </row>
@@ -2224,13 +2224,13 @@
       <c r="B114" t="inlineStr"/>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MTDR</t>
+          <t>NAT</t>
         </is>
       </c>
       <c r="D114" t="inlineStr"/>
       <c r="E114" t="inlineStr">
         <is>
-          <t>VAL</t>
+          <t>VLO</t>
         </is>
       </c>
     </row>
@@ -2239,13 +2239,13 @@
       <c r="B115" t="inlineStr"/>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NAT</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
-          <t>VIRT</t>
+          <t>W</t>
         </is>
       </c>
     </row>
@@ -2254,13 +2254,13 @@
       <c r="B116" t="inlineStr"/>
       <c r="C116" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>NEM</t>
         </is>
       </c>
       <c r="D116" t="inlineStr"/>
       <c r="E116" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>WELL</t>
         </is>
       </c>
     </row>
@@ -2269,13 +2269,13 @@
       <c r="B117" t="inlineStr"/>
       <c r="C117" t="inlineStr">
         <is>
-          <t>NEM</t>
+          <t>NLY</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>W</t>
+          <t>WMS</t>
         </is>
       </c>
     </row>
@@ -2284,13 +2284,13 @@
       <c r="B118" t="inlineStr"/>
       <c r="C118" t="inlineStr">
         <is>
-          <t>NLY</t>
+          <t>NRIX</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>WELL</t>
+          <t>WST</t>
         </is>
       </c>
     </row>
@@ -2299,13 +2299,13 @@
       <c r="B119" t="inlineStr"/>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NRIX</t>
+          <t>NTR</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>WES</t>
+          <t>ZM</t>
         </is>
       </c>
     </row>
@@ -2314,52 +2314,40 @@
       <c r="B120" t="inlineStr"/>
       <c r="C120" t="inlineStr">
         <is>
-          <t>NTR</t>
+          <t>NUVB</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>WMS</t>
-        </is>
-      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr"/>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NUVB</t>
+          <t>NVS</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>WST</t>
-        </is>
-      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>NVS</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>ZM</t>
-        </is>
-      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr"/>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -2370,7 +2358,7 @@
       <c r="B124" t="inlineStr"/>
       <c r="C124" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>OBE</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -2381,7 +2369,7 @@
       <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>OBE</t>
+          <t>OCUL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -2392,7 +2380,7 @@
       <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>OCUL</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -2403,7 +2391,7 @@
       <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>OMER</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
@@ -2414,7 +2402,7 @@
       <c r="B128" t="inlineStr"/>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OMER</t>
+          <t>ONC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -2425,7 +2413,7 @@
       <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>ORC</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -2436,7 +2424,7 @@
       <c r="B130" t="inlineStr"/>
       <c r="C130" t="inlineStr">
         <is>
-          <t>ORC</t>
+          <t>ORIC</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -2447,7 +2435,7 @@
       <c r="B131" t="inlineStr"/>
       <c r="C131" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>OSCR</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -2458,7 +2446,7 @@
       <c r="B132" t="inlineStr"/>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OSCR</t>
+          <t>OVID</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -2469,7 +2457,7 @@
       <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>OVID</t>
+          <t>OVV</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -2480,7 +2468,7 @@
       <c r="B134" t="inlineStr"/>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OVV</t>
+          <t>OXY</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -2491,7 +2479,7 @@
       <c r="B135" t="inlineStr"/>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OXY</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -2502,7 +2490,7 @@
       <c r="B136" t="inlineStr"/>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>PCG</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -2513,7 +2501,7 @@
       <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PCG</t>
+          <t>PCVX</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -2524,7 +2512,7 @@
       <c r="B138" t="inlineStr"/>
       <c r="C138" t="inlineStr">
         <is>
-          <t>PCVX</t>
+          <t>PHVS</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
@@ -2535,7 +2523,7 @@
       <c r="B139" t="inlineStr"/>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PHVS</t>
+          <t>PK</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -2546,7 +2534,7 @@
       <c r="B140" t="inlineStr"/>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PK</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -2557,7 +2545,7 @@
       <c r="B141" t="inlineStr"/>
       <c r="C141" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>PSNL</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -2568,7 +2556,7 @@
       <c r="B142" t="inlineStr"/>
       <c r="C142" t="inlineStr">
         <is>
-          <t>PSNL</t>
+          <t>PTEN</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
@@ -2579,7 +2567,7 @@
       <c r="B143" t="inlineStr"/>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PTEN</t>
+          <t>QURE</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
@@ -2590,7 +2578,7 @@
       <c r="B144" t="inlineStr"/>
       <c r="C144" t="inlineStr">
         <is>
-          <t>QURE</t>
+          <t>RCUS</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
@@ -2601,7 +2589,7 @@
       <c r="B145" t="inlineStr"/>
       <c r="C145" t="inlineStr">
         <is>
-          <t>RCUS</t>
+          <t>RIO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
@@ -2612,7 +2600,7 @@
       <c r="B146" t="inlineStr"/>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RIO</t>
+          <t>RLAY</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -2623,7 +2611,7 @@
       <c r="B147" t="inlineStr"/>
       <c r="C147" t="inlineStr">
         <is>
-          <t>RLAY</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
@@ -2634,7 +2622,7 @@
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr">
         <is>
-          <t>ROIV</t>
+          <t>RPRX</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
@@ -2645,7 +2633,7 @@
       <c r="B149" t="inlineStr"/>
       <c r="C149" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>RSG</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
@@ -2656,7 +2644,7 @@
       <c r="B150" t="inlineStr"/>
       <c r="C150" t="inlineStr">
         <is>
-          <t>RSG</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
@@ -2667,7 +2655,7 @@
       <c r="B151" t="inlineStr"/>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RVMD</t>
+          <t>SBLK</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
@@ -2678,7 +2666,7 @@
       <c r="B152" t="inlineStr"/>
       <c r="C152" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>SCCO</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>

--- a/results/latest.xlsx
+++ b/results/latest.xlsx
@@ -414,9 +414,895 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>1. 信號反轉-底背離</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2. 信號反轉-回升</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>3. 機會入場</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>4. 重新起漲</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>5. 空中加油</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ASTS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ABUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>CDZI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ACRS</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ABSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>CELC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AFRM</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ACHV</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ALM</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>IONS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMGN</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ASND</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LBTYA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMLX</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AVAH</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LOPE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ARGX</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AXGN</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>QUBT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>BIIB</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AUPH</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>CCEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CADL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>CERS</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CGAU</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>CHRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CGON</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>CLYM</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CORT</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>CNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CRON</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>COKE</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CVSA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CYRX</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>ETON</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>DJCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>FCFS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>DUOT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr"/>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>FRHC</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>FANG</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>FWONK</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr"/>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>FOX</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>GOLD</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr"/>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GRAL</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>FROG</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>IBKR</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GLNG</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>IDYA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ILMN</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>IMMX</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr"/>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>INBX</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>IMNM</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>INCY</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>IMVT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>MEDP</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>IRD</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MEOH</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>JAZZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>MRX</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>KOPN</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr"/>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>NDSN</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>KRNY</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr"/>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LPTH</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr"/>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>NWS</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>MGTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr"/>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>OMER</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>MU</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr"/>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>ONC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr"/>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PCAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr"/>
+      <c r="B42" t="inlineStr"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>PCVX</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr"/>
+      <c r="B43" t="inlineStr"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>PGEN</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr"/>
+      <c r="B44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>PHVS</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr"/>
+      <c r="B45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>PRLD</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>SATL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr"/>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PSNL</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SBUX</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>RFAI</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SLDB</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RPRX</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>TARS</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>RZLT</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SHC</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SLS</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>SOPH</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr"/>
+      <c r="B54" t="inlineStr"/>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>SRRK</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr"/>
+      <c r="B55" t="inlineStr"/>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>SRTA</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr"/>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SSRM</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr"/>
+      <c r="B57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>STOK</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr"/>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr"/>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TRLV</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -427,9 +1313,586 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>強勢+站穩+大量</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>開漲+站穩</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>開漲+大量</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>開漲</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ADBE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TMUS</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>GDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ADP</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ADPT</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>SOUN</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>HTZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ADSK</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>AMCR</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BR</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BMNR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ALM</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>BTU</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>BRZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ASST</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ARCC</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CAKE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CAI</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ARX</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CME</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AUGO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>AVTR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CMCSA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EXE</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BETA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BLSH</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DBX</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>FBRX</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BSY</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BNTX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>DFTX</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IBKR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CGAU</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DXCM</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ILMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CLBK</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CSX</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>FIVN</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>INFQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CPB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>FUTU</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GEHC</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MKTX</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>INTU</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>MRVL</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DASH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NDAQ</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>MDLZ</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DKNG</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>OCUL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NVAX</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PAA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIGR</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RGEN</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FROG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PSNL</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>GH</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>SBLK</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>HTFL</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RVMD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>SLS</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SSRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>NTRA</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>OMER</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>RELY</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PPC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SHC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SMCI</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/latest.xlsx
+++ b/results/latest.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABSI</t>
+          <t>AFRM</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
@@ -472,13 +472,13 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AFRM</t>
+          <t>AGYS</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ABUS</t>
+          <t>ABSI</t>
         </is>
       </c>
     </row>
@@ -486,18 +486,18 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IMTX</t>
+          <t>CTMX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AQST</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ACHV</t>
+          <t>ABUS</t>
         </is>
       </c>
     </row>
@@ -505,12 +505,12 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>INTR</t>
+          <t>IMTX</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AXGN</t>
+          <t>AVPT</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -529,13 +529,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AYA</t>
+          <t>AXGN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ARGX</t>
+          <t>AQST</t>
         </is>
       </c>
     </row>
@@ -544,13 +544,13 @@
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CACC</t>
+          <t>AYA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>ARGX</t>
         </is>
       </c>
     </row>
@@ -559,13 +559,13 @@
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CADL</t>
+          <t>BCRX</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AVAH</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
@@ -574,13 +574,13 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>BGC</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BGC</t>
+          <t>AVAH</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLPT</t>
+          <t>CHRD</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -610,7 +610,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CMPS</t>
+          <t>CACC</t>
         </is>
       </c>
     </row>
@@ -619,13 +619,13 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>COKE</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CRDO</t>
+          <t>CADL</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CRWD</t>
+          <t>CGAU</t>
         </is>
       </c>
     </row>
@@ -655,7 +655,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>CLPT</t>
         </is>
       </c>
     </row>
@@ -670,7 +670,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FCFS</t>
+          <t>CMPS</t>
         </is>
       </c>
     </row>
@@ -679,13 +679,13 @@
       <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EZPW</t>
+          <t>ETSY</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FRHC</t>
+          <t>CRDO</t>
         </is>
       </c>
     </row>
@@ -694,13 +694,13 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>EZPW</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FTNT</t>
+          <t>CRWD</t>
         </is>
       </c>
     </row>
@@ -709,13 +709,13 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>FRHC</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>CSX</t>
         </is>
       </c>
     </row>
@@ -724,13 +724,13 @@
       <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>FROG</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>HSIC</t>
+          <t>EXEL</t>
         </is>
       </c>
     </row>
@@ -739,13 +739,13 @@
       <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IMMX</t>
+          <t>FCFS</t>
         </is>
       </c>
     </row>
@@ -754,13 +754,13 @@
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IRON</t>
+          <t>GH</t>
         </is>
       </c>
     </row>
@@ -769,13 +769,13 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IBKR</t>
+          <t>GRAL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>GILD</t>
         </is>
       </c>
     </row>
@@ -784,13 +784,13 @@
       <c r="B23" t="inlineStr"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>IBKR</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>MELI</t>
+          <t>GMAB</t>
         </is>
       </c>
     </row>
@@ -799,13 +799,13 @@
       <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IDYA</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>HOOD</t>
         </is>
       </c>
     </row>
@@ -814,13 +814,13 @@
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>IFRX</t>
+          <t>ILMN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>NEXT</t>
+          <t>HSIC</t>
         </is>
       </c>
     </row>
@@ -829,13 +829,13 @@
       <c r="B26" t="inlineStr"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ILMN</t>
+          <t>INBX</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>NTRA</t>
+          <t>IDYA</t>
         </is>
       </c>
     </row>
@@ -844,13 +844,13 @@
       <c r="B27" t="inlineStr"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INBX</t>
+          <t>IRON</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>IFRX</t>
         </is>
       </c>
     </row>
@@ -859,13 +859,13 @@
       <c r="B28" t="inlineStr"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>KRYS</t>
+          <t>KRNY</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>NWS</t>
+          <t>IMMX</t>
         </is>
       </c>
     </row>
@@ -874,13 +874,13 @@
       <c r="B29" t="inlineStr"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>KRYS</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OKTA</t>
+          <t>JOYY</t>
         </is>
       </c>
     </row>
@@ -889,13 +889,13 @@
       <c r="B30" t="inlineStr"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MDGL</t>
+          <t>LECO</t>
         </is>
       </c>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>LPTH</t>
         </is>
       </c>
     </row>
@@ -904,13 +904,13 @@
       <c r="B31" t="inlineStr"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MRVL</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PSNL</t>
+          <t>LTRX</t>
         </is>
       </c>
     </row>
@@ -919,13 +919,13 @@
       <c r="B32" t="inlineStr"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NDAQ</t>
+          <t>MDGL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PVLA</t>
+          <t>MRVL</t>
         </is>
       </c>
     </row>
@@ -934,13 +934,13 @@
       <c r="B33" t="inlineStr"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>MEOH</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>QURE</t>
+          <t>NDAQ</t>
         </is>
       </c>
     </row>
@@ -949,13 +949,13 @@
       <c r="B34" t="inlineStr"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NWSA</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>REAX</t>
+          <t>NTRA</t>
         </is>
       </c>
     </row>
@@ -964,13 +964,13 @@
       <c r="B35" t="inlineStr"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PAA</t>
+          <t>NEXT</t>
         </is>
       </c>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RGLD</t>
+          <t>NVDA</t>
         </is>
       </c>
     </row>
@@ -979,13 +979,13 @@
       <c r="B36" t="inlineStr"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PAGP</t>
+          <t>NWS</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RPRX</t>
+          <t>OVID</t>
         </is>
       </c>
     </row>
@@ -994,13 +994,13 @@
       <c r="B37" t="inlineStr"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SBRA</t>
+          <t>NWSA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RVMD</t>
+          <t>PANW</t>
         </is>
       </c>
     </row>
@@ -1009,13 +1009,13 @@
       <c r="B38" t="inlineStr"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SBUX</t>
+          <t>OKTA</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RZLT</t>
+          <t>PHVS</t>
         </is>
       </c>
     </row>
@@ -1024,13 +1024,13 @@
       <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SHC</t>
+          <t>PAA</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SBLK</t>
+          <t>PLTR</t>
         </is>
       </c>
     </row>
@@ -1039,13 +1039,13 @@
       <c r="B40" t="inlineStr"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>PAGP</t>
         </is>
       </c>
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SLS</t>
+          <t>PTEN</t>
         </is>
       </c>
     </row>
@@ -1054,13 +1054,13 @@
       <c r="B41" t="inlineStr"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SLDB</t>
+          <t>ROIV</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SRRK</t>
+          <t>REAX</t>
         </is>
       </c>
     </row>
@@ -1069,13 +1069,13 @@
       <c r="B42" t="inlineStr"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SMTC</t>
+          <t>RVMD</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSRM</t>
+          <t>RGLD</t>
         </is>
       </c>
     </row>
@@ -1084,46 +1084,151 @@
       <c r="B43" t="inlineStr"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>TRMD</t>
+          <t>SBUX</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>RPRX</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>SLAB</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>TGTX</t>
+          <t>RZLT</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>SLDB</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TH</t>
+          <t>SBLK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>SLS</t>
+        </is>
+      </c>
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
+          <t>SBRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr"/>
+      <c r="B47" t="inlineStr"/>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>SMTC</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SEIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr"/>
+      <c r="B48" t="inlineStr"/>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TGTX</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SRRK</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr"/>
+      <c r="B49" t="inlineStr"/>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TH</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SSRM</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr"/>
+      <c r="B50" t="inlineStr"/>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TRMD</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr"/>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>TRLV</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr"/>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>VSXY</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr"/>
+      <c r="B53" t="inlineStr"/>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>XNCR</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1243,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,182 +1271,584 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABNB</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SKHY</t>
+          <t>BTBT</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ASST</t>
+          <t>AVTR</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SPCX</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FROG</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BULL</t>
+          <t>AVAH</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>SKHY</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BMNR</t>
+          <t>ADPT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>IONS</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CELH</t>
+          <t>SPCX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>BTU</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CTSH</t>
+          <t>ADSK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PURR</t>
+          <t>BSY</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CHYM</t>
+          <t>BRZE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>RVMD</t>
+          <t>DBX</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DLTR</t>
+          <t>ARCC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SHOP</t>
+          <t>BULL</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>COIN</t>
+          <t>CEG</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TEM</t>
+          <t>DOCU</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GEN</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>TEAM</t>
+          <t>CDNA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GTLB</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>CHYM</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FIVE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GLXY</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HOOD</t>
+          <t>GEN</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INFQ</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>DXCM</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>FROG</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PTEN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
+          <t>PEP</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GTLB</t>
+        </is>
+      </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MSTR</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr"/>
+          <t>EXE</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>GENB</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SLS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>BMNR</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>IBRX</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>EXLS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>GLXY</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>BLSH</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ILMN</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FRSH</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>MNDY</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>CCC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>KMB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CCEP</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>MRSH</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HTFL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>MTCH</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>MSTR</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LFST</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NAVN</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>CG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NCNO</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NESR</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NWSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>CHTR</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NTNX</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PGY</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PEGA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>COIN</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PLTR</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RIVN</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>SSNC</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PTEN</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TMC</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>STRC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>DAIC</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PURR</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TRMB</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TEAM</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EXEL</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>ROKU</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>XNCR</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIVN</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RVMD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SSRM</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PAYX</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SHOP</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PSKY</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FWONK</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SLS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>HALO</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>SRPT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>KURA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>INFQ</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ROIV</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ALM</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TEM</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SBET</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TRI</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>TECH</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>CRML</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TPG</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PAGP</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>RUM</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HOOD</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
